--- a/output/pdf_financials_xlsx/TUK.xlsx
+++ b/output/pdf_financials_xlsx/TUK.xlsx
@@ -5905,13 +5905,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>-0.094788</v>
+        <v>-0.121368</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.02193</v>
+        <v>0.013822</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.19205</v>
+        <v>0.187087</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>0</v>
@@ -27894,7 +27894,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E263" s="5" t="n">
         <v>-0.02658</v>
       </c>

--- a/output/pdf_financials_xlsx/TUK.xlsx
+++ b/output/pdf_financials_xlsx/TUK.xlsx
@@ -2000,22 +2000,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.014299</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.036737</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000821</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.019523</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.008696000000000001</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.060376</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.008305999999999999</v>
@@ -2092,22 +2092,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.014299</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.036737</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000821</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.019523</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.008696000000000001</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.060376</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.008305999999999999</v>
@@ -2644,22 +2644,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.014299</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.036737</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.000821</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.019523</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.010272</v>
+        <v>0.001576</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.060376</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
@@ -6219,7 +6219,7 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.051209</v>
       </c>
     </row>
     <row r="125">
@@ -6265,7 +6265,7 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.051209</v>
       </c>
     </row>
     <row r="126">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -14592,7 +14592,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
@@ -19406,7 +19406,11 @@
           <t>Lease payments 13</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TUK.xlsx
+++ b/output/pdf_financials_xlsx/TUK.xlsx
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-0</v>
+        <v>0.007013</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0</v>
+        <v>0.006527</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>0.005605</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>0.005914</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>0.006214</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>0.006625</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>0.0069</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>-0</v>
@@ -1677,25 +1677,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.103341</v>
+        <v>-0.110354</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.158825</v>
+        <v>-0.165352</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.310732</v>
+        <v>-0.316337</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.160475</v>
+        <v>-0.166389</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.135993</v>
+        <v>-0.142207</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.158253</v>
+        <v>-0.164878</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.125948</v>
+        <v>-0.132848</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.09137000000000001</v>
@@ -1769,25 +1769,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.090605</v>
+        <v>-0.097618</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.150594</v>
+        <v>-0.157121</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.308948</v>
+        <v>-0.314553</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.159064</v>
+        <v>-0.164978</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.134855</v>
+        <v>-0.141069</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.157317</v>
+        <v>-0.163942</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.12517</v>
+        <v>-0.13207</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.090714</v>
@@ -37190,7 +37190,11 @@
           <t>Net finance expense $</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
@@ -37591,7 +37595,11 @@
           <t>Net finance expense</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -38067,7 +38075,11 @@
           <t>Net finance expense (Note 13)</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -38472,7 +38484,11 @@
           <t>Net finance expense (Note 15)</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
@@ -39280,7 +39296,11 @@
           <t>Net finance expense (Note 17)</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E405" s="5" t="n">
         <v>-0.007013</v>
       </c>

--- a/output/pdf_financials_xlsx/TUK.xlsx
+++ b/output/pdf_financials_xlsx/TUK.xlsx
@@ -5567,13 +5567,13 @@
         <v>0</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.09465</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.108595</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.115188</v>
       </c>
     </row>
     <row r="111">
@@ -18144,7 +18144,11 @@
           <t>Accretion 12</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -20516,7 +20520,11 @@
           <t>Accretion 13</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -22130,7 +22138,11 @@
           <t>Accretion 11</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
